--- a/Data/1_DATA.xlsx
+++ b/Data/1_DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Lux_Project_Intern(KNIME)\Data of the tasks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Lux_Project_Intern\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{0673441A-018C-417F-A3F4-C96BFBC54317}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{79FA22B1-1953-48F6-A9D8-7EA4EB8170C0}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8952" xr2:uid="{65A2B071-1A6E-46E7-B634-5A08B92D1495}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="8928" xr2:uid="{65A2B071-1A6E-46E7-B634-5A08B92D1495}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -985,9 +985,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1">
-        <v>46022</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1000,9 +998,7 @@
       <c r="E2" s="1">
         <v>45430</v>
       </c>
-      <c r="F2" s="1">
-        <v>45986</v>
-      </c>
+      <c r="F2" s="1"/>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -1297,9 +1293,7 @@
       <c r="E13" s="1">
         <v>45734</v>
       </c>
-      <c r="F13" s="1">
-        <v>45964</v>
-      </c>
+      <c r="F13" s="1"/>
       <c r="G13" t="s">
         <v>12</v>
       </c>
@@ -1567,7 +1561,9 @@
       <c r="E23" s="1">
         <v>44607</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="F23" s="1">
+        <v>45964</v>
+      </c>
       <c r="G23" t="s">
         <v>38</v>
       </c>
@@ -1606,9 +1602,7 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="1">
-        <v>44742</v>
-      </c>
+      <c r="A25" s="1"/>
       <c r="B25" t="s">
         <v>41</v>
       </c>
@@ -2794,9 +2788,7 @@
       <c r="I68" s="2"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="1">
-        <v>45930</v>
-      </c>
+      <c r="A69" s="1"/>
       <c r="B69" t="s">
         <v>130</v>
       </c>
@@ -3127,9 +3119,7 @@
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="1">
-        <v>45838</v>
-      </c>
+      <c r="A82" s="1"/>
       <c r="B82" t="s">
         <v>154</v>
       </c>
